--- a/Result/profitability/6281.xlsx
+++ b/Result/profitability/6281.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02875</v>
+        <v>1.015</v>
       </c>
       <c r="N2" t="n">
-        <v>20.70625</v>
+        <v>20.77125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.98625</v>
+        <v>1.04125</v>
       </c>
       <c r="N3" t="n">
-        <v>21.07625</v>
+        <v>20.73375</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9849999999999999</v>
+        <v>0.98875</v>
       </c>
       <c r="N4" t="n">
-        <v>21.0125</v>
+        <v>20.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0.91375</v>
       </c>
       <c r="N5" t="n">
-        <v>21.40625</v>
+        <v>21.52875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.925</v>
+        <v>0.9637499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>22.04625</v>
+        <v>22.03375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9112499999999999</v>
+        <v>0.9712499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>22.4075</v>
+        <v>22.085</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.9075</v>
       </c>
       <c r="N8" t="n">
-        <v>22.2625</v>
+        <v>22.0025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5259</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4251</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>138</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>143</v>
+      </c>
+      <c r="K75" t="n">
+        <v>112</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.98625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.1725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.079999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09788235294117642</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.9800000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05387575590984062</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
